--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R2" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900808</v>
+        <v>128900807</v>
       </c>
       <c r="B3" t="n">
         <v>98632</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628334</v>
+        <v>628333</v>
       </c>
       <c r="R3" t="n">
-        <v>6987643</v>
+        <v>6987637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900807</v>
+        <v>128900813</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628333</v>
+        <v>628353</v>
       </c>
       <c r="R4" t="n">
-        <v>6987637</v>
+        <v>6987667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91800</v>
+        <v>91958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91958</v>
+        <v>91800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B10" t="n">
-        <v>91958</v>
+        <v>91800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R10" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91800</v>
+        <v>91958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91862</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>91862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900808</v>
+        <v>128900813</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628334</v>
+        <v>628353</v>
       </c>
       <c r="R2" t="n">
-        <v>6987643</v>
+        <v>6987667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900807</v>
+        <v>128900801</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628333</v>
+        <v>628361</v>
       </c>
       <c r="R3" t="n">
-        <v>6987637</v>
+        <v>6987563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900813</v>
+        <v>128900807</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628353</v>
+        <v>628333</v>
       </c>
       <c r="R4" t="n">
-        <v>6987667</v>
+        <v>6987637</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900801</v>
+        <v>128900808</v>
       </c>
       <c r="B5" t="n">
-        <v>91800</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628361</v>
+        <v>628334</v>
       </c>
       <c r="R5" t="n">
-        <v>6987563</v>
+        <v>6987643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128900800</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91800</v>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91958</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B14" t="n">
-        <v>91800</v>
+        <v>91508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R14" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B15" t="n">
-        <v>91504</v>
+        <v>91804</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R15" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>91866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R17" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2210,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>91862</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R18" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R2" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900801</v>
+        <v>128900807</v>
       </c>
       <c r="B3" t="n">
-        <v>91804</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628361</v>
+        <v>628333</v>
       </c>
       <c r="R3" t="n">
-        <v>6987563</v>
+        <v>6987637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900807</v>
+        <v>128900813</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628333</v>
+        <v>628353</v>
       </c>
       <c r="R4" t="n">
-        <v>6987637</v>
+        <v>6987667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900808</v>
+        <v>128900801</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>91804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628334</v>
+        <v>628361</v>
       </c>
       <c r="R5" t="n">
-        <v>6987643</v>
+        <v>6987563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B10" t="n">
-        <v>91962</v>
+        <v>91804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R10" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91508</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R14" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91804</v>
+        <v>91508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R15" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900808</v>
+        <v>128900801</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628334</v>
+        <v>628361</v>
       </c>
       <c r="R2" t="n">
-        <v>6987643</v>
+        <v>6987563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900807</v>
+        <v>128900813</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628333</v>
+        <v>628353</v>
       </c>
       <c r="R3" t="n">
-        <v>6987637</v>
+        <v>6987667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R4" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900801</v>
+        <v>128900807</v>
       </c>
       <c r="B5" t="n">
-        <v>91804</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628361</v>
+        <v>628333</v>
       </c>
       <c r="R5" t="n">
-        <v>6987563</v>
+        <v>6987637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91804</v>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91962</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900801</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900813</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128900808</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900807</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900800</v>
+        <v>128900795</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628395</v>
       </c>
       <c r="R9" t="n">
-        <v>6987546</v>
+        <v>6987566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900811</v>
+        <v>128900800</v>
       </c>
       <c r="B10" t="n">
-        <v>91962</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628353</v>
+        <v>628388</v>
       </c>
       <c r="R10" t="n">
-        <v>6987667</v>
+        <v>6987546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>91513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R14" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B15" t="n">
-        <v>91508</v>
+        <v>91809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R15" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900808</v>
+        <v>128900813</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628334</v>
+        <v>628353</v>
       </c>
       <c r="R2" t="n">
-        <v>6987643</v>
+        <v>6987667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900807</v>
+        <v>128900801</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>91805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628333</v>
+        <v>628361</v>
       </c>
       <c r="R3" t="n">
-        <v>6987637</v>
+        <v>6987563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R4" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900801</v>
+        <v>128900807</v>
       </c>
       <c r="B5" t="n">
-        <v>91805</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628361</v>
+        <v>628333</v>
       </c>
       <c r="R5" t="n">
-        <v>6987563</v>
+        <v>6987637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900813</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128900801</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128900808</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900807</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128900800</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91805</v>
+        <v>91978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91975</v>
+        <v>91808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900813</v>
+        <v>128900801</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628353</v>
+        <v>628361</v>
       </c>
       <c r="R2" t="n">
-        <v>6987667</v>
+        <v>6987563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900801</v>
+        <v>128900813</v>
       </c>
       <c r="B3" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628361</v>
+        <v>628353</v>
       </c>
       <c r="R3" t="n">
-        <v>6987563</v>
+        <v>6987667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128900808</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900807</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900800</v>
+        <v>128900795</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628395</v>
       </c>
       <c r="R9" t="n">
-        <v>6987546</v>
+        <v>6987566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900811</v>
+        <v>128900800</v>
       </c>
       <c r="B10" t="n">
-        <v>91978</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628353</v>
+        <v>628388</v>
       </c>
       <c r="R10" t="n">
-        <v>6987667</v>
+        <v>6987546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91808</v>
+        <v>91981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91882</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>91885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>91885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R17" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2210,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>91885</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R18" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900795</v>
+        <v>128900800</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628395</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6987566</v>
+        <v>6987546</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900800</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628388</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987546</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91981</v>
+        <v>91811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91885</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>91885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900801</v>
+        <v>128900808</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628361</v>
+        <v>628334</v>
       </c>
       <c r="R2" t="n">
-        <v>6987563</v>
+        <v>6987643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900813</v>
+        <v>128900807</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628353</v>
+        <v>628333</v>
       </c>
       <c r="R3" t="n">
-        <v>6987667</v>
+        <v>6987637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900808</v>
+        <v>128900801</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628334</v>
+        <v>628361</v>
       </c>
       <c r="R4" t="n">
-        <v>6987643</v>
+        <v>6987563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900807</v>
+        <v>128900813</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628333</v>
+        <v>628353</v>
       </c>
       <c r="R5" t="n">
-        <v>6987637</v>
+        <v>6987667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R14" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R15" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>91885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R17" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2210,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>91885</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R18" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900808</v>
+        <v>128900813</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628334</v>
+        <v>628353</v>
       </c>
       <c r="R2" t="n">
-        <v>6987643</v>
+        <v>6987667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900807</v>
+        <v>128900801</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628333</v>
+        <v>628361</v>
       </c>
       <c r="R3" t="n">
-        <v>6987637</v>
+        <v>6987563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900801</v>
+        <v>128900807</v>
       </c>
       <c r="B4" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628361</v>
+        <v>628333</v>
       </c>
       <c r="R4" t="n">
-        <v>6987563</v>
+        <v>6987637</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R5" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900800</v>
+        <v>128900795</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628395</v>
       </c>
       <c r="R9" t="n">
-        <v>6987546</v>
+        <v>6987566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900795</v>
+        <v>128900800</v>
       </c>
       <c r="B11" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628395</v>
+        <v>628388</v>
       </c>
       <c r="R11" t="n">
-        <v>6987566</v>
+        <v>6987546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R14" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R15" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91885</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>91892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900813</v>
+        <v>128900801</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628353</v>
+        <v>628361</v>
       </c>
       <c r="R2" t="n">
-        <v>6987667</v>
+        <v>6987563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900801</v>
+        <v>128900813</v>
       </c>
       <c r="B3" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628361</v>
+        <v>628353</v>
       </c>
       <c r="R3" t="n">
-        <v>6987563</v>
+        <v>6987667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128900807</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900808</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128900795</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900811</v>
+        <v>128900800</v>
       </c>
       <c r="B10" t="n">
-        <v>91988</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628353</v>
+        <v>628388</v>
       </c>
       <c r="R10" t="n">
-        <v>6987667</v>
+        <v>6987546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900800</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>91995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628388</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987546</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>91899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R17" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2210,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>91892</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R18" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900801</v>
+        <v>128900813</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628361</v>
+        <v>628353</v>
       </c>
       <c r="R2" t="n">
-        <v>6987563</v>
+        <v>6987667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900813</v>
+        <v>128900801</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628353</v>
+        <v>628361</v>
       </c>
       <c r="R3" t="n">
-        <v>6987667</v>
+        <v>6987563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128900807</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128900808</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B9" t="n">
-        <v>91825</v>
+        <v>91997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R9" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900800</v>
+        <v>128900795</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628388</v>
+        <v>628395</v>
       </c>
       <c r="R10" t="n">
-        <v>6987546</v>
+        <v>6987566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900800</v>
       </c>
       <c r="B11" t="n">
-        <v>91995</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628388</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R14" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R15" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91899</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>91901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900807</v>
+        <v>128900808</v>
       </c>
       <c r="B4" t="n">
         <v>98678</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628333</v>
+        <v>628334</v>
       </c>
       <c r="R4" t="n">
-        <v>6987637</v>
+        <v>6987643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900808</v>
+        <v>128900807</v>
       </c>
       <c r="B5" t="n">
         <v>98678</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628334</v>
+        <v>628333</v>
       </c>
       <c r="R5" t="n">
-        <v>6987643</v>
+        <v>6987637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900811</v>
+        <v>128900800</v>
       </c>
       <c r="B9" t="n">
-        <v>91997</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628353</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6987667</v>
+        <v>6987546</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900800</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628388</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987546</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R14" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R15" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>91901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R17" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2210,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>91901</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R18" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900813</v>
+        <v>128900807</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628353</v>
+        <v>628333</v>
       </c>
       <c r="R2" t="n">
-        <v>6987667</v>
+        <v>6987637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900801</v>
+        <v>128900808</v>
       </c>
       <c r="B3" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628361</v>
+        <v>628334</v>
       </c>
       <c r="R3" t="n">
-        <v>6987563</v>
+        <v>6987643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900808</v>
+        <v>128900813</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628334</v>
+        <v>628353</v>
       </c>
       <c r="R4" t="n">
-        <v>6987643</v>
+        <v>6987667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900807</v>
+        <v>128900801</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628333</v>
+        <v>628361</v>
       </c>
       <c r="R5" t="n">
-        <v>6987637</v>
+        <v>6987563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128900800</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128900795</v>
       </c>
       <c r="B10" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900807</v>
+        <v>128900813</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628333</v>
+        <v>628353</v>
       </c>
       <c r="R2" t="n">
-        <v>6987637</v>
+        <v>6987667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900808</v>
+        <v>128900801</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628334</v>
+        <v>628361</v>
       </c>
       <c r="R3" t="n">
-        <v>6987643</v>
+        <v>6987563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R4" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900801</v>
+        <v>128900807</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628361</v>
+        <v>628333</v>
       </c>
       <c r="R5" t="n">
-        <v>6987563</v>
+        <v>6987637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91837</v>
+        <v>91993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91992</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>91911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900813</v>
+        <v>128900801</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628353</v>
+        <v>628361</v>
       </c>
       <c r="R2" t="n">
-        <v>6987667</v>
+        <v>6987563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900801</v>
+        <v>128900808</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628361</v>
+        <v>628334</v>
       </c>
       <c r="R3" t="n">
-        <v>6987563</v>
+        <v>6987643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900808</v>
+        <v>128900807</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628334</v>
+        <v>628333</v>
       </c>
       <c r="R4" t="n">
-        <v>6987643</v>
+        <v>6987637</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900807</v>
+        <v>128900813</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628333</v>
+        <v>628353</v>
       </c>
       <c r="R5" t="n">
-        <v>6987637</v>
+        <v>6987667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900800</v>
+        <v>128900795</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628395</v>
       </c>
       <c r="R9" t="n">
-        <v>6987546</v>
+        <v>6987566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900811</v>
+        <v>128900800</v>
       </c>
       <c r="B10" t="n">
-        <v>91993</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628353</v>
+        <v>628388</v>
       </c>
       <c r="R10" t="n">
-        <v>6987667</v>
+        <v>6987546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900795</v>
+        <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>91993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R11" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128900801</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900808</v>
+        <v>128900813</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628334</v>
+        <v>628353</v>
       </c>
       <c r="R3" t="n">
-        <v>6987643</v>
+        <v>6987667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128900807</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900813</v>
+        <v>128900808</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628353</v>
+        <v>628334</v>
       </c>
       <c r="R5" t="n">
-        <v>6987667</v>
+        <v>6987643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128900795</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128900800</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128900811</v>
       </c>
       <c r="B11" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>91914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R17" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,6 +2210,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B18" t="n">
-        <v>91911</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2240,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R18" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,7 +2308,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R14" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R15" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128900801</v>
+        <v>128900808</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628361</v>
+        <v>628334</v>
       </c>
       <c r="R2" t="n">
-        <v>6987563</v>
+        <v>6987643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128900813</v>
+        <v>128900807</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628353</v>
+        <v>628333</v>
       </c>
       <c r="R3" t="n">
-        <v>6987667</v>
+        <v>6987637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128900807</v>
+        <v>128900801</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628333</v>
+        <v>628361</v>
       </c>
       <c r="R4" t="n">
-        <v>6987637</v>
+        <v>6987563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900808</v>
+        <v>128900813</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628334</v>
+        <v>628353</v>
       </c>
       <c r="R5" t="n">
-        <v>6987643</v>
+        <v>6987667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128900803</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128900806</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128900804</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900795</v>
+        <v>128900800</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628395</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6987566</v>
+        <v>6987546</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900800</v>
+        <v>128900811</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91998</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628388</v>
+        <v>628353</v>
       </c>
       <c r="R10" t="n">
-        <v>6987546</v>
+        <v>6987667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900811</v>
+        <v>128900795</v>
       </c>
       <c r="B11" t="n">
-        <v>91996</v>
+        <v>91843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R11" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128900799</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128900809</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900796</v>
+        <v>128900810</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628395</v>
+        <v>628353</v>
       </c>
       <c r="R14" t="n">
-        <v>6987566</v>
+        <v>6987667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900810</v>
+        <v>128900796</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628353</v>
+        <v>628395</v>
       </c>
       <c r="R15" t="n">
-        <v>6987667</v>
+        <v>6987566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>128900802</v>
       </c>
       <c r="B16" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900812</v>
+        <v>128900805</v>
       </c>
       <c r="B17" t="n">
-        <v>91914</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628353</v>
+        <v>628317</v>
       </c>
       <c r="R17" t="n">
-        <v>6987667</v>
+        <v>6987628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,7 +2210,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900805</v>
+        <v>128900812</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>91916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628317</v>
+        <v>628353</v>
       </c>
       <c r="R18" t="n">
-        <v>6987628</v>
+        <v>6987667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2307,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>128900794</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22047-2025 artfynd.xlsx
+++ b/artfynd/A 22047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900795</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900801</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900810</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900796</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900804</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900813</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900811</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900802</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900812</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2032,6 +2102,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900794</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2129,6 +2204,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900805</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2226,6 +2306,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900807</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2323,6 +2408,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900808</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2420,8 +2510,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>